--- a/empresas_clasificadas/G4S_RISK_MANAGEMENT_COLOMBIA_SA/REPORTE GUARDA/REPORTE_07_04_2026.xlsx
+++ b/empresas_clasificadas/G4S_RISK_MANAGEMENT_COLOMBIA_SA/REPORTE GUARDA/REPORTE_07_04_2026.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
   <si>
     <t>EMPRESA: G4S RISK MANAGEMENT COLOMBIA SA</t>
   </si>
   <si>
-    <t>FECHA: 07/04/2026 16:14:24</t>
+    <t>FECHA: 07/04/2026 19:00:15</t>
   </si>
   <si>
     <t>Nombre</t>
@@ -38,31 +38,25 @@
     <t>Fecha Nacimiento</t>
   </si>
   <si>
+    <t>Fecha Examen</t>
+  </si>
+  <si>
+    <t>Resultado</t>
+  </si>
+  <si>
     <t>Tipo Examen</t>
   </si>
   <si>
-    <t>PEDRO ANTONIO DUARTE</t>
+    <t>ROBINSON DANIEL PATACON HERNANDEZ</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>DEIBIS FERNANDO VANEGAS ATENCIO</t>
-  </si>
-  <si>
-    <t>CARLOS JULIO CASTIBLANCO DIAZ</t>
-  </si>
-  <si>
-    <t>ELVER DANIEL GONZALEZ HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
-    <t>ROBINSON DANIEL PATACON HERNANDEZ</t>
+    <t>Sin Resultado</t>
+  </si>
+  <si>
+    <t>Psicofisico</t>
   </si>
 </sst>
 </file>
@@ -420,7 +414,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="48.274" bestFit="true" customWidth="true" style="0"/>
@@ -428,20 +422,22 @@
     <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="16.282" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" customHeight="1" ht="25">
+    <row r="1" spans="1:8" customHeight="1" ht="25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" customHeight="1" ht="25">
+    <row r="2" spans="1:8" customHeight="1" ht="25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -460,105 +456,37 @@
       <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>74282993</v>
+        <v>1010206813</v>
       </c>
       <c r="C5">
-        <v>3212572859</v>
+        <v>3118821768</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>30682</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>9022573</v>
-      </c>
-      <c r="C6">
-        <v>3145348492</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>29879</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+        <v>33654</v>
+      </c>
+      <c r="F5">
+        <v>46112</v>
+      </c>
+      <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="B7">
-        <v>80471011</v>
-      </c>
-      <c r="C7">
-        <v>3208437949</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>26639</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="H5" t="s">
         <v>13</v>
-      </c>
-      <c r="B8">
-        <v>91507578</v>
-      </c>
-      <c r="C8">
-        <v>3013861341</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8">
-        <v>29999</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9">
-        <v>1010206813</v>
-      </c>
-      <c r="C9">
-        <v>3118821768</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9">
-        <v>33654</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
